--- a/datos_cristalizador.xlsx
+++ b/datos_cristalizador.xlsx
@@ -1,17 +1,132 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3f6bb513862a7542/Desktop/U/2026-2/Proyecto de título/Código PT/CristalizadorPT/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="11" documentId="11_1568710D69335AE6897C63A0B53B8EFBA15AD8AE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{94D1B612-C940-4CA0-B980-44716DE5F2F1}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="msmpr" sheetId="1" r:id="rId1"/>
     <sheet name="solubilidad" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
+</file>
+
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={9C0E0B2F-8ACE-49FC-B792-856A46D7CBCE}</author>
+    <author>tc={9E4CBFEA-00B7-4B6A-81B3-6CB536B3DAA4}</author>
+    <author>tc={C5A3C7D4-C246-4985-8241-8FE8FEEAB14E}</author>
+    <author>tc={D06A7FB6-D933-4502-BC95-B844B8CD9BE6}</author>
+    <author>tc={E96B9EC0-8FE3-4864-B326-1DD36A6B084F}</author>
+    <author>tc={CE96E9A4-ED71-4ADD-B323-E9091AD5E6B8}</author>
+    <author>tc={844F6EAD-B274-481D-888A-CDABF835194D}</author>
+    <author>tc={559F896F-6451-4BA7-86E4-377D49E83A90}</author>
+    <author>tc={94CF5F9A-FF33-4FB2-8D77-72ADB019357C}</author>
+    <author>tc={2AA542DC-58C8-4FAB-8743-124DBCCB3532}</author>
+    <author>tc={3F85ECEA-852C-4150-9989-C2116B743A83}</author>
+  </authors>
+  <commentList>
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{9C0E0B2F-8ACE-49FC-B792-856A46D7CBCE}">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Fracción de dilución: fracción del caudal de alimentación que es agua en vez de solución madre. Con d = 0,05, el 5 % es agua y la concentración de alimentación es C_f = (1−d)·220 kg/m³. </t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="1" shapeId="0" xr:uid="{9E4CBFEA-00B7-4B6A-81B3-6CB536B3DAA4}">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Temperatura del cristalizador. Fija la solubilidad C*(T). 
+</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="2" shapeId="0" xr:uid="{C5A3C7D4-C246-4985-8241-8FE8FEEAB14E}">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Tiempo de residencia τ = V/Q. El caso BASE es 660 m³ / 280,83 m³/h = 2,35 h. Se usan 0,8, 1,0 y 1,2 veces ese valor. </t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="3" shapeId="0" xr:uid="{D06A7FB6-D933-4502-BC95-B844B8CD9BE6}">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Producción de cristales de KNO₃ que salen del cristalizador. </t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="4" shapeId="0" xr:uid="{E96B9EC0-8FE3-4864-B326-1DD36A6B084F}">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Error típico de la medición de producción </t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="5" shapeId="0" xr:uid="{CE96E9A4-ED71-4ADD-B323-E9091AD5E6B8}">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Tamaño mediano en volumen: el 50 % del volumen de cristales es más chico que este tamaño. Se mide con granulometría (por ejemplo, difracción láser o tamizado). </t>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="6" shapeId="0" xr:uid="{844F6EAD-B274-481D-888A-CDABF835194D}">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Error típico del D50 </t>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="7" shapeId="0" xr:uid="{559F896F-6451-4BA7-86E4-377D49E83A90}">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Concentración de KNO₃ disuelto en el licor madre que sale. </t>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="8" shapeId="0" xr:uid="{94CF5F9A-FF33-4FB2-8D77-72ADB019357C}">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Error típico del análisis de concentración </t>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="9" shapeId="0" xr:uid="{2AA542DC-58C8-4FAB-8743-124DBCCB3532}">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Concentración de KNO₃ disuelto en el licor madre que sale. </t>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="10" shapeId="0" xr:uid="{3F85ECEA-852C-4150-9989-C2116B743A83}">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Error típico del análisis de impureza </t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -143,14 +258,20 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -181,13 +302,27 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Francisca Flores rojas" id="{91AADED8-45C1-469B-A4FA-480CFB7CBA45}" userId="3f6bb513862a7542" providerId="Windows Live"/>
+</personList>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -225,7 +360,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -259,6 +394,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -293,9 +429,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -467,12 +604,51 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="B1" dT="2026-10-25T23:07:29.53" personId="{91AADED8-45C1-469B-A4FA-480CFB7CBA45}" id="{9C0E0B2F-8ACE-49FC-B792-856A46D7CBCE}">
+    <text xml:space="preserve">Fracción de dilución: fracción del caudal de alimentación que es agua en vez de solución madre. Con d = 0,05, el 5 % es agua y la concentración de alimentación es C_f = (1−d)·220 kg/m³. </text>
+  </threadedComment>
+  <threadedComment ref="C1" dT="2026-10-25T23:07:52.96" personId="{91AADED8-45C1-469B-A4FA-480CFB7CBA45}" id="{9E4CBFEA-00B7-4B6A-81B3-6CB536B3DAA4}">
+    <text xml:space="preserve">Temperatura del cristalizador. Fija la solubilidad C*(T). 
+</text>
+  </threadedComment>
+  <threadedComment ref="D1" dT="2026-10-25T23:10:28.74" personId="{91AADED8-45C1-469B-A4FA-480CFB7CBA45}" id="{C5A3C7D4-C246-4985-8241-8FE8FEEAB14E}">
+    <text xml:space="preserve">Tiempo de residencia τ = V/Q. El caso BASE es 660 m³ / 280,83 m³/h = 2,35 h. Se usan 0,8, 1,0 y 1,2 veces ese valor. </text>
+  </threadedComment>
+  <threadedComment ref="E1" dT="2026-10-25T23:11:10.49" personId="{91AADED8-45C1-469B-A4FA-480CFB7CBA45}" id="{D06A7FB6-D933-4502-BC95-B844B8CD9BE6}">
+    <text xml:space="preserve">Producción de cristales de KNO₃ que salen del cristalizador. </text>
+  </threadedComment>
+  <threadedComment ref="F1" dT="2026-10-25T23:13:39.53" personId="{91AADED8-45C1-469B-A4FA-480CFB7CBA45}" id="{E96B9EC0-8FE3-4864-B326-1DD36A6B084F}">
+    <text xml:space="preserve">Error típico de la medición de producción </text>
+  </threadedComment>
+  <threadedComment ref="G1" dT="2026-10-25T23:11:27.40" personId="{91AADED8-45C1-469B-A4FA-480CFB7CBA45}" id="{CE96E9A4-ED71-4ADD-B323-E9091AD5E6B8}">
+    <text xml:space="preserve">Tamaño mediano en volumen: el 50 % del volumen de cristales es más chico que este tamaño. Se mide con granulometría (por ejemplo, difracción láser o tamizado). </text>
+  </threadedComment>
+  <threadedComment ref="H1" dT="2026-10-25T23:14:15.31" personId="{91AADED8-45C1-469B-A4FA-480CFB7CBA45}" id="{844F6EAD-B274-481D-888A-CDABF835194D}">
+    <text xml:space="preserve">Error típico del D50 </text>
+  </threadedComment>
+  <threadedComment ref="I1" dT="2026-10-25T23:11:39.11" personId="{91AADED8-45C1-469B-A4FA-480CFB7CBA45}" id="{559F896F-6451-4BA7-86E4-377D49E83A90}">
+    <text xml:space="preserve">Concentración de KNO₃ disuelto en el licor madre que sale. </text>
+  </threadedComment>
+  <threadedComment ref="J1" dT="2026-10-25T23:15:52.79" personId="{91AADED8-45C1-469B-A4FA-480CFB7CBA45}" id="{94CF5F9A-FF33-4FB2-8D77-72ADB019357C}">
+    <text xml:space="preserve">Error típico del análisis de concentración </text>
+  </threadedComment>
+  <threadedComment ref="K1" dT="2026-10-25T23:11:54.28" personId="{91AADED8-45C1-469B-A4FA-480CFB7CBA45}" id="{2AA542DC-58C8-4FAB-8743-124DBCCB3532}">
+    <text xml:space="preserve">Concentración de KNO₃ disuelto en el licor madre que sale. </text>
+  </threadedComment>
+  <threadedComment ref="L1" dT="2026-10-25T23:16:10.75" personId="{91AADED8-45C1-469B-A4FA-480CFB7CBA45}" id="{3F85ECEA-852C-4150-9989-C2116B743A83}">
+    <text xml:space="preserve">Error típico del análisis de impureza </text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L28"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -510,7 +686,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -527,13 +703,13 @@
         <v>14993.22857754697</v>
       </c>
       <c r="F2">
-        <v>227.606222825333</v>
+        <v>227.60622282533299</v>
       </c>
       <c r="G2">
-        <v>166.9690914125794</v>
+        <v>166.96909141257939</v>
       </c>
       <c r="H2">
-        <v>4.973180609105379</v>
+        <v>4.9731806091053787</v>
       </c>
       <c r="I2">
         <v>175.8264027221191</v>
@@ -542,13 +718,13 @@
         <v>0.5</v>
       </c>
       <c r="K2">
-        <v>0.03906460823270947</v>
+        <v>3.906460823270947E-2</v>
       </c>
       <c r="L2">
-        <v>0.001825809732969478</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
+        <v>1.8258097329694779E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -559,34 +735,34 @@
         <v>35</v>
       </c>
       <c r="D3">
-        <v>2.350176263219741</v>
+        <v>2.3501762632197409</v>
       </c>
       <c r="E3">
         <v>12506.227111569</v>
       </c>
       <c r="F3">
-        <v>185.8143419150339</v>
+        <v>185.81434191503391</v>
       </c>
       <c r="G3">
-        <v>172.4298176479205</v>
+        <v>172.42981764792049</v>
       </c>
       <c r="H3">
-        <v>5.218617049002133</v>
+        <v>5.2186170490021331</v>
       </c>
       <c r="I3">
-        <v>175.7332710405996</v>
+        <v>175.73327104059959</v>
       </c>
       <c r="J3">
         <v>0.5</v>
       </c>
       <c r="K3">
-        <v>0.03707062479130276</v>
+        <v>3.7070624791302763E-2</v>
       </c>
       <c r="L3">
-        <v>0.001825794196998466</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
+        <v>1.8257941969984661E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -603,28 +779,28 @@
         <v>10426.03396867779</v>
       </c>
       <c r="F4">
-        <v>157.0209335882163</v>
+        <v>157.02093358821631</v>
       </c>
       <c r="G4">
-        <v>179.6181272156929</v>
+        <v>179.61812721569291</v>
       </c>
       <c r="H4">
-        <v>5.425312602213399</v>
+        <v>5.4253126022133991</v>
       </c>
       <c r="I4">
-        <v>175.6295012769895</v>
+        <v>175.62950127698949</v>
       </c>
       <c r="J4">
         <v>0.5</v>
       </c>
       <c r="K4">
-        <v>0.03745540660044647</v>
+        <v>3.7455406600446467E-2</v>
       </c>
       <c r="L4">
-        <v>0.001825783321024999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
+        <v>1.825783321024999E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -638,16 +814,16 @@
         <v>1.880141010575793</v>
       </c>
       <c r="E5">
-        <v>12073.2423562798</v>
+        <v>12073.242356279799</v>
       </c>
       <c r="F5">
         <v>181.273005298437</v>
       </c>
       <c r="G5">
-        <v>158.0719782516196</v>
+        <v>158.07197825161961</v>
       </c>
       <c r="H5">
-        <v>4.754350914839988</v>
+        <v>4.7543509148399883</v>
       </c>
       <c r="I5">
         <v>185.6543154951259</v>
@@ -656,13 +832,13 @@
         <v>0.5</v>
       </c>
       <c r="K5">
-        <v>0.0353981076375995</v>
+        <v>3.5398107637599499E-2</v>
       </c>
       <c r="L5">
-        <v>0.001825964161009583</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
+        <v>1.8259641610095831E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -673,19 +849,19 @@
         <v>40</v>
       </c>
       <c r="D6">
-        <v>2.350176263219741</v>
+        <v>2.3501762632197409</v>
       </c>
       <c r="E6">
-        <v>9855.980860791087</v>
+        <v>9855.9808607910873</v>
       </c>
       <c r="F6">
         <v>148.7405232965578</v>
       </c>
       <c r="G6">
-        <v>169.1985857946267</v>
+        <v>169.19858579462669</v>
       </c>
       <c r="H6">
-        <v>4.993820191102039</v>
+        <v>4.9938201911020386</v>
       </c>
       <c r="I6">
         <v>184.6250161111206</v>
@@ -694,13 +870,13 @@
         <v>0.5</v>
       </c>
       <c r="K6">
-        <v>0.03400934142851825</v>
+        <v>3.4009341428518247E-2</v>
       </c>
       <c r="L6">
-        <v>0.001825948652605011</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
+        <v>1.825948652605011E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -717,28 +893,28 @@
         <v>8348.208345381081</v>
       </c>
       <c r="F7">
-        <v>126.1260846234376</v>
+        <v>126.12608462343761</v>
       </c>
       <c r="G7">
-        <v>176.5779024259699</v>
+        <v>176.57790242596991</v>
       </c>
       <c r="H7">
         <v>5.195002545452132</v>
       </c>
       <c r="I7">
-        <v>183.9543389188941</v>
+        <v>183.95433891889411</v>
       </c>
       <c r="J7">
         <v>0.5</v>
       </c>
       <c r="K7">
-        <v>0.03624717863965812</v>
+        <v>3.6247178639658123E-2</v>
       </c>
       <c r="L7">
-        <v>0.001825937774811122</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
+        <v>1.8259377748111221E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -752,31 +928,31 @@
         <v>1.880141010575793</v>
       </c>
       <c r="E8">
-        <v>8955.807893065417</v>
+        <v>8955.8078930654174</v>
       </c>
       <c r="F8">
-        <v>133.0561140816849</v>
+        <v>133.05611408168491</v>
       </c>
       <c r="G8">
-        <v>157.2435881853794</v>
+        <v>157.24358818537939</v>
       </c>
       <c r="H8">
-        <v>4.472491047921019</v>
+        <v>4.4724910479210189</v>
       </c>
       <c r="I8">
-        <v>194.3742888003628</v>
+        <v>194.37428880036279</v>
       </c>
       <c r="J8">
         <v>0.5</v>
       </c>
       <c r="K8">
-        <v>0.03898449192663316</v>
+        <v>3.8984491926633162E-2</v>
       </c>
       <c r="L8">
-        <v>0.00182612489504743</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
+        <v>1.82612489504743E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -787,7 +963,7 @@
         <v>45</v>
       </c>
       <c r="D9">
-        <v>2.350176263219741</v>
+        <v>2.3501762632197409</v>
       </c>
       <c r="E9">
         <v>7203.60228242624</v>
@@ -796,25 +972,25 @@
         <v>110.0851259049636</v>
       </c>
       <c r="G9">
-        <v>157.6634656575924</v>
+        <v>157.66346565759241</v>
       </c>
       <c r="H9">
-        <v>4.705204803198664</v>
+        <v>4.7052048031986642</v>
       </c>
       <c r="I9">
-        <v>193.2819574183789</v>
+        <v>193.28195741837891</v>
       </c>
       <c r="J9">
         <v>0.5</v>
       </c>
       <c r="K9">
-        <v>0.03899010543683078</v>
+        <v>3.8990105436830777E-2</v>
       </c>
       <c r="L9">
-        <v>0.001826109725148788</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
+        <v>1.826109725148788E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>20</v>
       </c>
@@ -831,28 +1007,28 @@
         <v>6336.435775676171</v>
       </c>
       <c r="F10">
-        <v>93.8723025572814</v>
+        <v>93.872302557281401</v>
       </c>
       <c r="G10">
         <v>168.9155484984293</v>
       </c>
       <c r="H10">
-        <v>4.900214757608508</v>
+        <v>4.9002147576085084</v>
       </c>
       <c r="I10">
-        <v>192.815844497669</v>
+        <v>192.81584449766899</v>
       </c>
       <c r="J10">
         <v>0.5</v>
       </c>
       <c r="K10">
-        <v>0.03777204628634526</v>
+        <v>3.7772046286345257E-2</v>
       </c>
       <c r="L10">
-        <v>0.001826099050224073</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
+        <v>1.826099050224073E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>21</v>
       </c>
@@ -869,28 +1045,28 @@
         <v>11332.86645001513</v>
       </c>
       <c r="F11">
-        <v>171.3268102241796</v>
+        <v>171.32681022417961</v>
       </c>
       <c r="G11">
-        <v>154.5682526167263</v>
+        <v>154.56825261672631</v>
       </c>
       <c r="H11">
-        <v>4.701560317361468</v>
+        <v>4.7015603173614684</v>
       </c>
       <c r="I11">
-        <v>176.7160399694608</v>
+        <v>176.71603996946081</v>
       </c>
       <c r="J11">
         <v>0.5</v>
       </c>
       <c r="K11">
-        <v>0.03621478976171733</v>
+        <v>3.6214789761717332E-2</v>
       </c>
       <c r="L11">
-        <v>0.001734697449212865</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12">
+        <v>1.7346974492128649E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -901,19 +1077,19 @@
         <v>35</v>
       </c>
       <c r="D12">
-        <v>2.350176263219741</v>
+        <v>2.3501762632197409</v>
       </c>
       <c r="E12">
-        <v>9399.527039545843</v>
+        <v>9399.5270395458429</v>
       </c>
       <c r="F12">
         <v>140.5619001844851</v>
       </c>
       <c r="G12">
-        <v>161.500397177443</v>
+        <v>161.50039717744301</v>
       </c>
       <c r="H12">
-        <v>4.938042729473749</v>
+        <v>4.9380427294737492</v>
       </c>
       <c r="I12">
         <v>175.218885292566</v>
@@ -922,13 +1098,13 @@
         <v>0.5</v>
       </c>
       <c r="K12">
-        <v>0.03719910491051911</v>
+        <v>3.7199104910519108E-2</v>
       </c>
       <c r="L12">
-        <v>0.001734683593127284</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12">
+        <v>1.7346835931272839E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>23</v>
       </c>
@@ -942,31 +1118,31 @@
         <v>2.82021151586369</v>
       </c>
       <c r="E13">
-        <v>8016.182032098831</v>
+        <v>8016.1820320988309</v>
       </c>
       <c r="F13">
-        <v>119.1809251347025</v>
+        <v>119.18092513470251</v>
       </c>
       <c r="G13">
         <v>174.9378184194081</v>
       </c>
       <c r="H13">
-        <v>5.137212687974945</v>
+        <v>5.1372126879749453</v>
       </c>
       <c r="I13">
-        <v>176.1406911520233</v>
+        <v>176.14069115202329</v>
       </c>
       <c r="J13">
         <v>0.5</v>
       </c>
       <c r="K13">
-        <v>0.03327822135021676</v>
+        <v>3.3278221350216762E-2</v>
       </c>
       <c r="L13">
-        <v>0.001734673874624456</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12">
+        <v>1.7346738746244559E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>24</v>
       </c>
@@ -980,31 +1156,31 @@
         <v>1.880141010575793</v>
       </c>
       <c r="E14">
-        <v>8685.824084796397</v>
+        <v>8685.8240847963971</v>
       </c>
       <c r="F14">
         <v>125.4703213839272</v>
       </c>
       <c r="G14">
-        <v>161.279192464513</v>
+        <v>161.27919246451299</v>
       </c>
       <c r="H14">
-        <v>4.420516529333646</v>
+        <v>4.4205165293336464</v>
       </c>
       <c r="I14">
-        <v>185.980732120598</v>
+        <v>185.98073212059799</v>
       </c>
       <c r="J14">
         <v>0.5</v>
       </c>
       <c r="K14">
-        <v>0.03613175323008332</v>
+        <v>3.6131753230083323E-2</v>
       </c>
       <c r="L14">
-        <v>0.001734842676074083</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12">
+        <v>1.7348426760740829E-3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -1015,34 +1191,34 @@
         <v>40</v>
       </c>
       <c r="D15">
-        <v>2.350176263219741</v>
+        <v>2.3501762632197409</v>
       </c>
       <c r="E15">
-        <v>6850.962277574353</v>
+        <v>6850.9622775743528</v>
       </c>
       <c r="F15">
-        <v>103.7979848821878</v>
+        <v>103.79798488218781</v>
       </c>
       <c r="G15">
-        <v>159.6382564965164</v>
+        <v>159.63825649651639</v>
       </c>
       <c r="H15">
-        <v>4.650404870672619</v>
+        <v>4.6504048706726193</v>
       </c>
       <c r="I15">
-        <v>184.1378902220654</v>
+        <v>184.13789022206541</v>
       </c>
       <c r="J15">
         <v>0.5</v>
       </c>
       <c r="K15">
-        <v>0.03465902216600172</v>
+        <v>3.4659022166001717E-2</v>
       </c>
       <c r="L15">
-        <v>0.001734829129340122</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12">
+        <v>1.734829129340122E-3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>26</v>
       </c>
@@ -1056,16 +1232,16 @@
         <v>2.82021151586369</v>
       </c>
       <c r="E16">
-        <v>5874.617088142087</v>
+        <v>5874.6170881420867</v>
       </c>
       <c r="F16">
-        <v>88.50482739565405</v>
+        <v>88.504827395654047</v>
       </c>
       <c r="G16">
-        <v>162.825952228458</v>
+        <v>162.82595222845799</v>
       </c>
       <c r="H16">
-        <v>4.843536345547157</v>
+        <v>4.8435363455471574</v>
       </c>
       <c r="I16">
         <v>184.4316818258483</v>
@@ -1074,13 +1250,13 @@
         <v>0.5</v>
       </c>
       <c r="K16">
-        <v>0.03373255382618709</v>
+        <v>3.3732553826187089E-2</v>
       </c>
       <c r="L16">
-        <v>0.00173481959687424</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12">
+        <v>1.73481959687424E-3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>27</v>
       </c>
@@ -1094,31 +1270,31 @@
         <v>1.880141010575793</v>
       </c>
       <c r="E17">
-        <v>5130.783888795025</v>
+        <v>5130.7838887950247</v>
       </c>
       <c r="F17">
-        <v>78.11640135235558</v>
+        <v>78.116401352355581</v>
       </c>
       <c r="G17">
-        <v>130.1649819380256</v>
+        <v>130.16498193802559</v>
       </c>
       <c r="H17">
-        <v>4.026089235439119</v>
+        <v>4.0260892354391187</v>
       </c>
       <c r="I17">
-        <v>193.6805229742999</v>
+        <v>193.68052297429989</v>
       </c>
       <c r="J17">
         <v>0.5</v>
       </c>
       <c r="K17">
-        <v>0.03221690022796784</v>
+        <v>3.2216900227967839E-2</v>
       </c>
       <c r="L17">
-        <v>0.001734992670800782</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12">
+        <v>1.734992670800782E-3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>28</v>
       </c>
@@ -1129,34 +1305,34 @@
         <v>45</v>
       </c>
       <c r="D18">
-        <v>2.350176263219741</v>
+        <v>2.3501762632197409</v>
       </c>
       <c r="E18">
-        <v>4319.904833524154</v>
+        <v>4319.9048335241541</v>
       </c>
       <c r="F18">
-        <v>65.69824500073555</v>
+        <v>65.698245000735554</v>
       </c>
       <c r="G18">
-        <v>147.1324214356702</v>
+        <v>147.13242143567021</v>
       </c>
       <c r="H18">
-        <v>4.249115590265528</v>
+        <v>4.2491155902655278</v>
       </c>
       <c r="I18">
-        <v>193.1071363430181</v>
+        <v>193.10713634301811</v>
       </c>
       <c r="J18">
         <v>0.5</v>
       </c>
       <c r="K18">
-        <v>0.03514567622715689</v>
+        <v>3.5145676227156891E-2</v>
       </c>
       <c r="L18">
-        <v>0.00173497997940857</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12">
+        <v>1.7349799794085701E-3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>29</v>
       </c>
@@ -1170,31 +1346,31 @@
         <v>2.82021151586369</v>
       </c>
       <c r="E19">
-        <v>3707.119703902781</v>
+        <v>3707.1197039027811</v>
       </c>
       <c r="F19">
-        <v>56.64068110461243</v>
+        <v>56.640681104612433</v>
       </c>
       <c r="G19">
-        <v>148.561248203903</v>
+        <v>148.56124820390301</v>
       </c>
       <c r="H19">
-        <v>4.434269156104058</v>
+        <v>4.4342691561040581</v>
       </c>
       <c r="I19">
-        <v>191.9943869326113</v>
+        <v>191.99438693261129</v>
       </c>
       <c r="J19">
         <v>0.5</v>
       </c>
       <c r="K19">
-        <v>0.03348709856351658</v>
+        <v>3.348709856351658E-2</v>
       </c>
       <c r="L19">
-        <v>0.00173497098869103</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12">
+        <v>1.73497098869103E-3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>30</v>
       </c>
@@ -1208,31 +1384,31 @@
         <v>1.880141010575793</v>
       </c>
       <c r="E20">
-        <v>7962.735317415192</v>
+        <v>7962.7353174151922</v>
       </c>
       <c r="F20">
         <v>115.5338948123694</v>
       </c>
       <c r="G20">
-        <v>142.429755856934</v>
+        <v>142.42975585693401</v>
       </c>
       <c r="H20">
-        <v>4.348951889887641</v>
+        <v>4.3489518898876414</v>
       </c>
       <c r="I20">
-        <v>176.6185726561445</v>
+        <v>176.61857265614449</v>
       </c>
       <c r="J20">
         <v>0.5</v>
       </c>
       <c r="K20">
-        <v>0.03361921066763526</v>
+        <v>3.3619210667635263E-2</v>
       </c>
       <c r="L20">
-        <v>0.001643564982130599</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12">
+        <v>1.643564982130599E-3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>31</v>
       </c>
@@ -1243,19 +1419,19 @@
         <v>35</v>
       </c>
       <c r="D21">
-        <v>2.350176263219741</v>
+        <v>2.3501762632197409</v>
       </c>
       <c r="E21">
-        <v>6360.415980805413</v>
+        <v>6360.4159808054128</v>
       </c>
       <c r="F21">
         <v>95.62568024731037</v>
       </c>
       <c r="G21">
-        <v>149.5373978588489</v>
+        <v>149.53739785884889</v>
       </c>
       <c r="H21">
-        <v>4.575636039969658</v>
+        <v>4.5756360399696581</v>
       </c>
       <c r="I21">
         <v>175.9427270094919</v>
@@ -1264,13 +1440,13 @@
         <v>0.5</v>
       </c>
       <c r="K21">
-        <v>0.03257952058485884</v>
+        <v>3.2579520584858843E-2</v>
       </c>
       <c r="L21">
-        <v>0.001643552984952078</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12">
+        <v>1.643552984952078E-3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>32</v>
       </c>
@@ -1284,7 +1460,7 @@
         <v>2.82021151586369</v>
       </c>
       <c r="E22">
-        <v>5562.190492440684</v>
+        <v>5562.1904924406836</v>
       </c>
       <c r="F22">
         <v>81.56411206681986</v>
@@ -1293,22 +1469,22 @@
         <v>155.4383433789059</v>
       </c>
       <c r="H22">
-        <v>4.765963432222105</v>
+        <v>4.7659634322221054</v>
       </c>
       <c r="I22">
-        <v>174.793513042338</v>
+        <v>174.79351304233799</v>
       </c>
       <c r="J22">
         <v>0.5</v>
       </c>
       <c r="K22">
-        <v>0.03363595936969954</v>
+        <v>3.3635959369699542E-2</v>
       </c>
       <c r="L22">
-        <v>0.001643544541049977</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12">
+        <v>1.643544541049977E-3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>33</v>
       </c>
@@ -1322,31 +1498,31 @@
         <v>1.880141010575793</v>
       </c>
       <c r="E23">
-        <v>4730.693520390562</v>
+        <v>4730.6935203905623</v>
       </c>
       <c r="F23">
-        <v>70.56541974224609</v>
+        <v>70.565419742246092</v>
       </c>
       <c r="G23">
         <v>126.6713702426138</v>
       </c>
       <c r="H23">
-        <v>3.946206161107673</v>
+        <v>3.9462061611076731</v>
       </c>
       <c r="I23">
-        <v>184.2666616047592</v>
+        <v>184.26666160475921</v>
       </c>
       <c r="J23">
         <v>0.5</v>
       </c>
       <c r="K23">
-        <v>0.03255186590594492</v>
+        <v>3.2551865905944923E-2</v>
       </c>
       <c r="L23">
-        <v>0.001643699928431441</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12">
+        <v>1.6436999284314411E-3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>34</v>
       </c>
@@ -1357,34 +1533,34 @@
         <v>40</v>
       </c>
       <c r="D24">
-        <v>2.350176263219741</v>
+        <v>2.3501762632197409</v>
       </c>
       <c r="E24">
-        <v>3911.48360252033</v>
+        <v>3911.4836025203299</v>
       </c>
       <c r="F24">
-        <v>59.43332688955174</v>
+        <v>59.433326889551743</v>
       </c>
       <c r="G24">
-        <v>141.6861629325742</v>
+        <v>141.68616293257421</v>
       </c>
       <c r="H24">
-        <v>4.165934134245283</v>
+        <v>4.1659341342452834</v>
       </c>
       <c r="I24">
-        <v>184.1850404884032</v>
+        <v>184.18504048840319</v>
       </c>
       <c r="J24">
         <v>0.5</v>
       </c>
       <c r="K24">
-        <v>0.02965693721841612</v>
+        <v>2.965693721841612E-2</v>
       </c>
       <c r="L24">
-        <v>0.001643688745485697</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12">
+        <v>1.643688745485697E-3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>35</v>
       </c>
@@ -1401,28 +1577,28 @@
         <v>3326.657245931483</v>
       </c>
       <c r="F25">
-        <v>51.28869558674634</v>
+        <v>51.288695586746343</v>
       </c>
       <c r="G25">
-        <v>139.3605320077047</v>
+        <v>139.36053200770471</v>
       </c>
       <c r="H25">
-        <v>4.347982397289909</v>
+        <v>4.3479823972899094</v>
       </c>
       <c r="I25">
-        <v>183.4480267377701</v>
+        <v>183.44802673777011</v>
       </c>
       <c r="J25">
         <v>0.5</v>
       </c>
       <c r="K25">
-        <v>0.03621550305668839</v>
+        <v>3.6215503056688393E-2</v>
       </c>
       <c r="L25">
-        <v>0.00164368081842568</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12">
+        <v>1.6436808184256801E-3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>36</v>
       </c>
@@ -1445,22 +1621,22 @@
         <v>108.4486491056779</v>
       </c>
       <c r="H26">
-        <v>3.229177618795709</v>
+        <v>3.2291776187957089</v>
       </c>
       <c r="I26">
-        <v>192.6230160848424</v>
+        <v>192.62301608484239</v>
       </c>
       <c r="J26">
         <v>0.5</v>
       </c>
       <c r="K26">
-        <v>0.0311558767590368</v>
+        <v>3.1155876759036801E-2</v>
       </c>
       <c r="L26">
-        <v>0.001643835146151837</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12">
+        <v>1.6438351461518369E-3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>37</v>
       </c>
@@ -1471,34 +1647,34 @@
         <v>45</v>
       </c>
       <c r="D27">
-        <v>2.350176263219741</v>
+        <v>2.3501762632197409</v>
       </c>
       <c r="E27">
-        <v>1474.317234376082</v>
+        <v>1474.3172343760821</v>
       </c>
       <c r="F27">
         <v>22.7836504307908</v>
       </c>
       <c r="G27">
-        <v>114.8316629147293</v>
+        <v>114.83166291472931</v>
       </c>
       <c r="H27">
-        <v>3.447881715846218</v>
+        <v>3.4478817158462181</v>
       </c>
       <c r="I27">
-        <v>193.0649624392543</v>
+        <v>193.06496243925429</v>
       </c>
       <c r="J27">
         <v>0.5</v>
       </c>
       <c r="K27">
-        <v>0.03229014852500782</v>
+        <v>3.229014852500782E-2</v>
       </c>
       <c r="L27">
-        <v>0.00164382624433293</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12">
+        <v>1.6438262443329299E-3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>38</v>
       </c>
@@ -1521,32 +1697,33 @@
         <v>121.5954525586551</v>
       </c>
       <c r="H28">
-        <v>3.626338914200368</v>
+        <v>3.6263389142003679</v>
       </c>
       <c r="I28">
-        <v>192.1631139826295</v>
+        <v>192.16311398262951</v>
       </c>
       <c r="J28">
         <v>0.5</v>
       </c>
       <c r="K28">
-        <v>0.03372666744547752</v>
+        <v>3.3726667445477518E-2</v>
       </c>
       <c r="L28">
-        <v>0.001643819763691088</v>
+        <v>1.6438197636910879E-3</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1557,40 +1734,40 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>25</v>
       </c>
       <c r="B2">
-        <v>155.3049765421684</v>
+        <v>155.30497654216839</v>
       </c>
       <c r="C2">
-        <v>0.7746371787825521</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>0.77463717878255212</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>30</v>
       </c>
       <c r="B3">
-        <v>163.8054555839313</v>
+        <v>163.80545558393129</v>
       </c>
       <c r="C3">
-        <v>0.8143536762323637</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>0.81435367623236365</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4">
         <v>35</v>
       </c>
       <c r="B4">
-        <v>170.5347381660332</v>
+        <v>170.53473816603321</v>
       </c>
       <c r="C4">
-        <v>0.8561064820506427</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+        <v>0.85610648205064266</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>40</v>
       </c>
@@ -1601,18 +1778,18 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>45</v>
       </c>
       <c r="B6">
-        <v>189.3373642466401</v>
+        <v>189.33736424664011</v>
       </c>
       <c r="C6">
-        <v>0.9461439867384218</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
+        <v>0.94614398673842182</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>50</v>
       </c>
@@ -1620,18 +1797,18 @@
         <v>198.3223602199424</v>
       </c>
       <c r="C7">
-        <v>0.994653826268083</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
+        <v>0.99465382626808296</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>55</v>
       </c>
       <c r="B8">
-        <v>209.1017458219659</v>
+        <v>209.10174582196589</v>
       </c>
       <c r="C8">
-        <v>1.045650818455455</v>
+        <v>1.0456508184554549</v>
       </c>
     </row>
   </sheetData>
